--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -28,7 +28,7 @@
     <t xml:space="preserve">Załącznik do pisma do Ministerstwa Kultury i Dziedzictwa Narodowego. Kwoty netto, z arkusza budżetowego pierwszej edycji.</t>
   </si>
   <si>
-    <t xml:space="preserve">Prośba o wskazanie drogi finansowania dotyczy wyłącznie wierszy oznaczonych "tak" w ostatniej kolumnie.</t>
+    <t xml:space="preserve">Ostatnia kolumna mówi, czy pozycja mieści się w zakresie pytania do Ministerstwa, a nie czy wnoszę o jej sfinansowanie. Objaśnienie pod tabelą.</t>
   </si>
   <si>
     <t xml:space="preserve">Działanie</t>
@@ -346,11 +346,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -394,11 +394,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -669,16 +669,31 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
@@ -1002,28 +1017,63 @@
       <c r="A24" s="14" t="s">
         <v>54</v>
       </c>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
         <v>55</v>
       </c>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
         <v>56</v>
       </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
         <v>57</v>
       </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
         <v>58</v>
       </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -196,7 +196,7 @@
     <t xml:space="preserve">"tak" - pozycja należy do części artystycznej przedsięwzięcia, której dotyczy pytanie o właściwy Program Ministra i o drogę finansowania. Jest to pytanie o tryb, nie o środki.</t>
   </si>
   <si>
-    <t xml:space="preserve">"nie" - pozycja jest poza tym pytaniem i ma być finansowana ze źródeł prywatnych. Wymieniam ją, aby było widoczne, że o tę samą pozycję nie zwracam się jednocześnie do dwóch źródeł.</t>
+    <t xml:space="preserve">"nie" - pozycja jest poza tym pytaniem i ma być finansowana z innych źródeł. Wymieniam ją, aby było widoczne, że o tę samą pozycję nie zwracam się jednocześnie do dwóch źródeł.</t>
   </si>
 </sst>
 </file>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -991,8 +991,8 @@
       <c r="E19" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>13</v>
+      <c r="F19" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>dziesięć nagrań, prawa przy autorach</t>
+          <t>możliwość realizacji nagrania studyjnego dla każdego z dziesięciu finalistów; liczba nagrań zależy od przyjęcia oferty, prawa przy autorach</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>511996.8</v>
+        <v>523196.8</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>77156.8</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>434840</v>
+        <v>446040</v>
       </c>
       <c r="G6" s="26" t="inlineStr">
         <is>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>523196.8</v>
+        <v>532156.8</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>77156.8</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>446040</v>
+        <v>455000</v>
       </c>
       <c r="G6" s="26" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>99600</v>
+        <v>107600</v>
       </c>
       <c r="E10" s="25" t="n">
         <v>28080</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>71520</v>
+        <v>79520</v>
       </c>
       <c r="G10" s="26" t="inlineStr">
         <is>
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>149552</v>
+        <v>157552</v>
       </c>
       <c r="E14" s="25" t="n">
         <v>17248</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>132304</v>
+        <v>140304</v>
       </c>
       <c r="G14" s="26" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D17" s="25" t="n">
-        <v>256800</v>
+        <v>264800</v>
       </c>
       <c r="E17" s="25" t="n">
         <v>32032</v>
       </c>
       <c r="F17" s="25" t="n">
-        <v>224768</v>
+        <v>232768</v>
       </c>
       <c r="G17" s="26" t="inlineStr">
         <is>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>532156.8</v>
+        <v>529516.8</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>77156.8</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>455000</v>
+        <v>452360</v>
       </c>
       <c r="G6" s="26" t="inlineStr">
         <is>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>e-book bezpłatny, Archiwum, egzemplarze dla laureatów</t>
+          <t>e-book bezpłatny, audiobook, Archiwum, egzemplarze dla laureatów</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>292422</v>
+        <v>344422</v>
       </c>
       <c r="E8" s="25" t="n">
         <v>201812</v>
       </c>
       <c r="F8" s="25" t="n">
-        <v>90610</v>
+        <v>142610</v>
       </c>
       <c r="G8" s="26" t="inlineStr">
         <is>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="46" customWidth="1" style="16" min="1" max="1"/>
@@ -673,12 +673,12 @@
     <row r="8" ht="23.25" customHeight="1" s="17">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>Antologia i Archiwum, w tym krótki nakład na galę</t>
+          <t>Antologia, Archiwum i podcast</t>
         </is>
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>e-book bezpłatny, audiobook, Archiwum, egzemplarze dla laureatów</t>
+          <t>e-book bezpłatny, audiobook, wydanie książkowe, Archiwum</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>344422</v>
+        <v>180362</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>201812</v>
+        <v>37752</v>
       </c>
       <c r="F8" s="25" t="n">
         <v>142610</v>
@@ -709,31 +709,33 @@
     <row r="9" ht="23.25" customHeight="1" s="17">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>Pierwsza runda oceny: Akademia rozmów i akademia filmu</t>
+          <t>Uruchomienie: fundacja, znak towarowy, strona i narzędzia oceny</t>
         </is>
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>przesiew zgłoszeń, dwa odczyty rozmowy i dwa obejrzenia filmu na zgłoszenie</t>
+          <t>fundacja w KRS, regulamin po konsultacji prawnej, cztery narzędzia, przebudowana strona</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>2027-2028</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>160160</v>
+        <v>164060</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>59360</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>100800</v>
+        <v>164060</v>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G9" s="26" t="inlineStr">
         <is>
-          <t>sponsor akademii</t>
+          <t>mecenas założycielski</t>
         </is>
       </c>
       <c r="H9" s="27" t="inlineStr">
@@ -745,12 +747,12 @@
     <row r="10" ht="23.25" customHeight="1" s="17">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>Plebiscyt na piosenkę: nabór, ocena, nagrody, prowadzenie</t>
+          <t>Pierwsza runda oceny: Akademia rozmów i akademia filmu</t>
         </is>
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>plebiscyt i jego laureaci</t>
+          <t>przesiew zgłoszeń, dwa odczyty rozmowy i dwa obejrzenia filmu na zgłoszenie</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -759,51 +761,49 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>107600</v>
+        <v>160160</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>28080</v>
+        <v>59360</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>79520</v>
+        <v>100800</v>
       </c>
       <c r="G10" s="26" t="inlineStr">
         <is>
-          <t>sponsor plebiscytu</t>
-        </is>
-      </c>
-      <c r="H10" s="29" t="inlineStr">
-        <is>
-          <t>tak</t>
+          <t>sponsor akademii</t>
+        </is>
+      </c>
+      <c r="H10" s="27" t="inlineStr">
+        <is>
+          <t>nie</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="17">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>Nagrania studyjne dziesiątki finalistów</t>
+          <t>Plebiscyt na piosenkę: nabór, ocena, nagrody, prowadzenie</t>
         </is>
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>możliwość realizacji nagrania studyjnego dla każdego z dziesięciu finalistów; liczba nagrań zależy od przyjęcia oferty, prawa przy autorach</t>
+          <t>plebiscyt i jego laureaci</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2027-2028</t>
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E11" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>107600</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>28080</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>75000</v>
+        <v>79520</v>
       </c>
       <c r="G11" s="26" t="inlineStr">
         <is>
@@ -819,29 +819,29 @@
     <row r="12" ht="15" customHeight="1" s="17">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>Hymn z teledyskiem</t>
+          <t>Nagrania studyjne dziesiątki finalistów</t>
         </is>
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>nagranie i premiera w czasie trwania naboru</t>
+          <t>możliwość realizacji nagrania studyjnego dla każdego z dziesięciu finalistów; liczba nagrań zależy od przyjęcia oferty, prawa przy autorach</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E12" s="25" t="n">
-        <v>80000</v>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
+        <v>75000</v>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>75000</v>
       </c>
       <c r="G12" s="26" t="inlineStr">
         <is>
@@ -857,32 +857,28 @@
     <row r="13" ht="15" customHeight="1" s="17">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>Realizacja części artystycznej gali</t>
+          <t>Hymn z teledyskiem</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>koncert finałowy</t>
+          <t>nagranie i premiera w czasie trwania naboru</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>do wyceny</t>
-        </is>
-      </c>
-      <c r="E13" s="31" t="inlineStr">
-        <is>
-          <t>do wyceny</t>
-        </is>
-      </c>
-      <c r="F13" s="31" t="inlineStr">
-        <is>
-          <t>do wyceny</t>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>80000</v>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G13" s="26" t="inlineStr">
@@ -899,31 +895,37 @@
     <row r="14" ht="23.25" customHeight="1" s="17">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>Plebiscyt na plakat: nabór, ocena, nagrody, oryginały</t>
+          <t>Realizacja części artystycznej gali</t>
         </is>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>plebiscyt, okładka antologii, Archiwum reprodukcji</t>
+          <t>koncert finałowy</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>2027-2028</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="n">
-        <v>157552</v>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>17248</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>140304</v>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>do wyceny</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>do wyceny</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>do wyceny</t>
+        </is>
       </c>
       <c r="G14" s="26" t="inlineStr">
         <is>
-          <t>mecenas plebiscytu na plakat o sztucznej inteligencji</t>
+          <t>sponsor plebiscytu</t>
         </is>
       </c>
       <c r="H14" s="29" t="inlineStr">
@@ -935,33 +937,27 @@
     <row r="15" ht="23.25" customHeight="1" s="17">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>Wystawa przy gali</t>
+          <t>Plebiscyt na plakat: nabór, ocena, nagrody, oryginały</t>
         </is>
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>dziesięć prac finałowych pokazanych publicznie</t>
+          <t>plebiscyt, okładka antologii, Archiwum reprodukcji</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
         <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="inlineStr">
-        <is>
-          <t>do wyceny</t>
-        </is>
-      </c>
-      <c r="E15" s="31" t="inlineStr">
-        <is>
-          <t>do wyceny</t>
-        </is>
-      </c>
-      <c r="F15" s="31" t="inlineStr">
-        <is>
-          <t>do wyceny</t>
-        </is>
+          <t>2027-2028</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="n">
+        <v>157552</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>17248</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>140304</v>
       </c>
       <c r="G15" s="26" t="inlineStr">
         <is>
@@ -977,12 +973,12 @@
     <row r="16" ht="23.25" customHeight="1" s="17">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>Wystawa w galerii sztuki z cichą licytacją, otwierana wernisażem</t>
+          <t>Wystawa przy gali</t>
         </is>
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
-          <t>te same prace pokazane po gali, jeżeli galeria zostanie pozyskana</t>
+          <t>dziesięć prac finałowych pokazanych publicznie</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
@@ -990,94 +986,94 @@
           <t>2028</t>
         </is>
       </c>
-      <c r="D16" s="32" t="n">
-        <v>4928</v>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>do wyceny</t>
+        </is>
       </c>
       <c r="E16" s="31" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="31" t="n">
-        <v>4928</v>
+          <t>do wyceny</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>do wyceny</t>
+        </is>
       </c>
       <c r="G16" s="26" t="inlineStr">
         <is>
-          <t>partner galerii</t>
-        </is>
-      </c>
-      <c r="H16" s="27" t="inlineStr">
-        <is>
-          <t>nie</t>
+          <t>mecenas plebiscytu na plakat o sztucznej inteligencji</t>
+        </is>
+      </c>
+      <c r="H16" s="29" t="inlineStr">
+        <is>
+          <t>tak</t>
         </is>
       </c>
     </row>
     <row r="17" ht="23.25" customHeight="1" s="17">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>Plebiscyt na film: nabór, ocena, nagrody, prowadzenie</t>
+          <t>Wystawa w galerii sztuki z cichą licytacją, otwierana wernisażem</t>
         </is>
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>plebiscyt, dziesięć filmów finałowych, Projektornia i Archiwum</t>
+          <t>te same prace pokazane po gali, jeżeli galeria zostanie pozyskana</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
-          <t>2027-2028</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="n">
-        <v>264800</v>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>32032</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>232768</v>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>4928</v>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>4928</v>
       </c>
       <c r="G17" s="26" t="inlineStr">
         <is>
-          <t>sponsor plebiscytu na film o sztucznej inteligencji</t>
-        </is>
-      </c>
-      <c r="H17" s="29" t="inlineStr">
-        <is>
-          <t>tak</t>
+          <t>partner galerii</t>
+        </is>
+      </c>
+      <c r="H17" s="27" t="inlineStr">
+        <is>
+          <t>nie</t>
         </is>
       </c>
     </row>
     <row r="18" ht="23.25" customHeight="1" s="17">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>Zwiastuny piątki na gali, a przy pozyskaniu sali także pełne pokazy filmów finałowych</t>
+          <t>Plebiscyt na film: nabór, ocena, nagrody, prowadzenie</t>
         </is>
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>zwiastuny pięciu filmów na gali, a przy pozyskaniu sali pełne pokazy dziesiątki</t>
+          <t>plebiscyt, dziesięć filmów finałowych, Projektornia i Archiwum</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="D18" s="31" t="inlineStr">
-        <is>
-          <t>do wyceny</t>
-        </is>
-      </c>
-      <c r="E18" s="31" t="inlineStr">
-        <is>
-          <t>do wyceny</t>
-        </is>
-      </c>
-      <c r="F18" s="31" t="inlineStr">
-        <is>
-          <t>do wyceny</t>
-        </is>
+          <t>2027-2028</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="n">
+        <v>264800</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>32032</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>232768</v>
       </c>
       <c r="G18" s="26" t="inlineStr">
         <is>
@@ -1093,113 +1089,158 @@
     <row r="19" ht="15" customHeight="1" s="17">
       <c r="A19" s="26" t="inlineStr">
         <is>
+          <t>Zwiastuny piątki na gali, a przy pozyskaniu sali także pełne pokazy filmów finałowych</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>zwiastuny pięciu filmów na gali, a przy pozyskaniu sali pełne pokazy dziesiątki</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>do wyceny</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>do wyceny</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>do wyceny</t>
+        </is>
+      </c>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>sponsor plebiscytu na film o sztucznej inteligencji</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="inlineStr">
+        <is>
+          <t>tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
           <t>Podcast towarzyszący Nagrodzie</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>bezpłatny materiał edukacyjny</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="D19" s="31" t="inlineStr">
+      <c r="D20" s="31" t="inlineStr">
         <is>
           <t>do wyceny</t>
         </is>
       </c>
-      <c r="E19" s="31" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>do wyceny</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr">
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>do wyceny</t>
         </is>
       </c>
-      <c r="G19" s="26" t="inlineStr">
+      <c r="G20" s="26" t="inlineStr">
         <is>
           <t>sponsor Antologii</t>
         </is>
       </c>
-      <c r="H19" s="29" t="inlineStr">
+      <c r="H20" s="29" t="inlineStr">
         <is>
           <t>tak</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="17">
-      <c r="A21" s="33" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="17"/>
+    <row r="22" ht="15" customHeight="1" s="17">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>Razem, wiersze objęte prośbą ("tak")</t>
         </is>
       </c>
-      <c r="D21" s="35">
-        <f>SUMIFS(D6:D19,$H$6:$H$19,"tak")</f>
+      <c r="D22" s="35">
+        <f>SUMIFS(D6:D20,$H$6:$H$20,"tak")</f>
         <v/>
       </c>
-      <c r="E21" s="35">
-        <f>SUMIFS(E6:E19,$H$6:$H$19,"tak")</f>
+      <c r="E22" s="35">
+        <f>SUMIFS(E6:E20,$H$6:$H$20,"tak")</f>
         <v/>
       </c>
-      <c r="F21" s="35">
-        <f>SUMIFS(F6:F19,$H$6:$H$19,"tak")</f>
+      <c r="F22" s="35">
+        <f>SUMIFS(F6:F20,$H$6:$H$20,"tak")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="17">
-      <c r="A22" s="36" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>Razem, wszystkie wycenione pozycje</t>
         </is>
       </c>
-      <c r="D22" s="38">
-        <f>SUM(D6:D19)</f>
+      <c r="D23" s="38">
+        <f>SUM(D6:D20)</f>
         <v/>
       </c>
-      <c r="E22" s="38">
-        <f>SUM(E6:E19)</f>
+      <c r="E23" s="38">
+        <f>SUM(E6:E20)</f>
         <v/>
       </c>
-      <c r="F22" s="38">
-        <f>SUM(F6:F19)</f>
+      <c r="F23" s="38">
+        <f>SUM(F6:F20)</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="17">
-      <c r="A24" s="39" t="inlineStr">
+    <row r="24" ht="15" customHeight="1" s="17"/>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>Pozycje opisane jako "do wyceny" nie wchodzą do sum powyżej; ich wycena powstanie przed złożeniem wniosku.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="17">
-      <c r="A26" s="40" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="17"/>
+    <row r="27" ht="15" customHeight="1" s="17">
+      <c r="A27" s="40" t="inlineStr">
         <is>
           <t>Co oznacza kolumna "W zakresie pytania do MKiDN"</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="17">
-      <c r="A27" s="39" t="inlineStr">
-        <is>
-          <t>Pismo nie jest wnioskiem o dotację i nie zawiera prośby o żadną z kwot wymienionych w tabeli.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="17">
       <c r="A28" s="39" t="inlineStr">
         <is>
-          <t>"tak" - pozycja należy do części artystycznej przedsięwzięcia, której dotyczy pytanie o właściwy Program Ministra i o drogę finansowania. Jest to pytanie o tryb, nie o środki.</t>
+          <t>Pismo nie jest wnioskiem o dotację i nie zawiera prośby o żadną z kwot wymienionych w tabeli.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="17">
       <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t>"tak" - pozycja należy do części artystycznej przedsięwzięcia, której dotyczy pytanie o właściwy Program Ministra i o drogę finansowania. Jest to pytanie o tryb, nie o środki.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="inlineStr">
         <is>
           <t>"nie" - pozycja jest poza tym pytaniem i ma być finansowana z innych źródeł. Wymieniam ją, aby było widoczne, że o tę samą pozycję nie zwracam się jednocześnie do dwóch źródeł.</t>
         </is>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>fundacja w KRS, regulamin po konsultacji prawnej, cztery narzędzia, przebudowana strona</t>
+          <t>fundacja w KRS, regulamin po konsultacji prawnej, cztery narzędzia, instalowalna wersja mobilna, przebudowana strona</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>164060</v>
+        <v>198380</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>164060</v>
+        <v>198380</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>180362</v>
+        <v>162162</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>37752</v>
+        <v>33942.4</v>
       </c>
       <c r="F8" s="25" t="n">
-        <v>142610</v>
+        <v>128219.6</v>
       </c>
       <c r="G8" s="26" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>198380</v>
+        <v>183480</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>198380</v>
+        <v>183480</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>529516.8</v>
+        <v>544449.76</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>77156.8</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>452360</v>
+        <v>467292.96</v>
       </c>
       <c r="G6" s="26" t="inlineStr">
         <is>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>544449.76</v>
+        <v>547809.76</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>77156.8</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>467292.96</v>
+        <v>470652.96</v>
       </c>
       <c r="G6" s="26" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>35168</v>
+        <v>62048</v>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="F7" s="25" t="n">
-        <v>35168</v>
+        <v>62048</v>
       </c>
       <c r="G7" s="26" t="inlineStr">
         <is>
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>107600</v>
+        <v>110960</v>
       </c>
       <c r="E11" s="25" t="n">
         <v>28080</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>79520</v>
+        <v>82880</v>
       </c>
       <c r="G11" s="26" t="inlineStr">
         <is>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>157552</v>
+        <v>160912</v>
       </c>
       <c r="E15" s="25" t="n">
         <v>17248</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>140304</v>
+        <v>143664</v>
       </c>
       <c r="G15" s="26" t="inlineStr">
         <is>
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>264800</v>
+        <v>268160</v>
       </c>
       <c r="E18" s="25" t="n">
         <v>32032</v>
       </c>
       <c r="F18" s="25" t="n">
-        <v>232768</v>
+        <v>236128</v>
       </c>
       <c r="G18" s="26" t="inlineStr">
         <is>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -381,7 +381,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -709,8 +709,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -749,7 +749,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
         <v>56</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>537672</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
         <v>60</v>
       </c>
@@ -1222,7 +1222,7 @@
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
         <v>61</v>
       </c>
@@ -1273,7 +1273,7 @@
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
         <v>65</v>
       </c>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
   <si>
     <t xml:space="preserve">Nagroda Konstela - zestawienie zadania: co, w którym roku, z czego i o co pytam</t>
   </si>
@@ -58,7 +58,7 @@
     <t xml:space="preserve">W zakresie pytania do MKiDN</t>
   </si>
   <si>
-    <t xml:space="preserve">Plebiscyt na rozmowę: nabór, ocena, prowadzenie</t>
+    <t xml:space="preserve">Plebiscyt na rozmowę: nabór, ocena, nagrody i prowadzenie</t>
   </si>
   <si>
     <t xml:space="preserve">laureat i dziesiątka finalistów</t>
@@ -91,16 +91,16 @@
     <t xml:space="preserve">Antologia, Archiwum i podcast</t>
   </si>
   <si>
-    <t xml:space="preserve">e-book bezpłatny, audiobook, wydanie książkowe, Archiwum</t>
+    <t xml:space="preserve">e-book bezpłatny, audiobook, wydanie książkowe, publiczne Archiwum</t>
   </si>
   <si>
     <t xml:space="preserve">partner wydawniczy lub sponsor organizacyjny</t>
   </si>
   <si>
-    <t xml:space="preserve">Uruchomienie: fundacja, znak towarowy, strona i narzędzia oceny</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fundacja w KRS, regulamin po konsultacji prawnej, cztery narzędzia, instalowalna wersja mobilna, przebudowana strona</t>
+    <t xml:space="preserve">Uruchomienie: fundacja, znak towarowy, strona i narzędzia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fundacja w KRS, regulamin po konsultacji, narzędzia dla czterech plebiscytów</t>
   </si>
   <si>
     <t xml:space="preserve">2027</t>
@@ -109,16 +109,16 @@
     <t xml:space="preserve">mecenas założycielski</t>
   </si>
   <si>
-    <t xml:space="preserve">Pierwsza runda oceny: Akademia rozmów i akademia filmu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">przesiew zgłoszeń, dwa odczyty rozmowy i dwa obejrzenia filmu na zgłoszenie</t>
+    <t xml:space="preserve">Pierwsza runda oceny: Akademia rozmów i filmów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">przesiew zgłoszeń, dwa odczyty rozmowy i dwa obejrzenia filmu</t>
   </si>
   <si>
     <t xml:space="preserve">sponsor akademii</t>
   </si>
   <si>
-    <t xml:space="preserve">Plebiscyt na piosenkę: nabór, ocena, nagrody, prowadzenie</t>
+    <t xml:space="preserve">Plebiscyt na piosenkę: nabór, ocena, nagrody i prowadzenie</t>
   </si>
   <si>
     <t xml:space="preserve">plebiscyt i jego laureaci</t>
@@ -133,10 +133,13 @@
     <t xml:space="preserve">Nagrania studyjne dziesiątki finalistów</t>
   </si>
   <si>
-    <t xml:space="preserve">możliwość realizacji nagrania studyjnego dla każdego z dziesięciu finalistów; liczba nagrań zależy od przyjęcia oferty, prawa przy autorach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hymn z teledyskiem</t>
+    <t xml:space="preserve">możliwość realizacji nagrania studyjnego dla każdego finalisty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sponsor plebiscytu albo mecenas muzyczny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hymn Nagrody z teledyskiem</t>
   </si>
   <si>
     <t xml:space="preserve">nagranie i premiera w czasie trwania naboru</t>
@@ -151,43 +154,55 @@
     <t xml:space="preserve">do wyceny</t>
   </si>
   <si>
-    <t xml:space="preserve">Plebiscyt na plakat: nabór, ocena, nagrody, oryginały</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plebiscyt, okładka antologii, Archiwum reprodukcji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mecenas plebiscytu na plakat o sztucznej inteligencji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wystawa przy gali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dziesięć prac finałowych pokazanych publicznie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wystawa w galerii sztuki z cichą licytacją, otwierana wernisażem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">te same prace pokazane po gali, jeżeli galeria zostanie pozyskana</t>
+    <t xml:space="preserve">Plebiscyt na plakat: nabór, ocena, nagrody i obieg oryginałów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plebiscyt, okładka antologii, Archiwum prac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mecenas plebiscytu na plakat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wystawa prac finałowych przy gali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dziesięć prac pokazanych publiczności w dniu rozstrzygnięcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wystawa w galerii sztuki z cichą licytacją</t>
+  </si>
+  <si>
+    <t xml:space="preserve">te same prace pokazane po gali, jeżeli znajdzie się galeria</t>
   </si>
   <si>
     <t xml:space="preserve">partner galerii</t>
   </si>
   <si>
-    <t xml:space="preserve">Plebiscyt na film: nabór, ocena, nagrody, prowadzenie</t>
+    <t xml:space="preserve">Plebiscyt na film: nabór, ocena, nagrody i prowadzenie</t>
   </si>
   <si>
     <t xml:space="preserve">plebiscyt, dziesięć filmów finałowych, Projektornia i Archiwum</t>
   </si>
   <si>
-    <t xml:space="preserve">sponsor plebiscytu na film o sztucznej inteligencji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zwiastuny piątki na gali, a przy pozyskaniu sali także pełne pokazy filmów finałowych</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zwiastuny pięciu filmów na gali, a przy pozyskaniu sali pełne pokazy dziesiątki</t>
+    <t xml:space="preserve">sponsor plebiscytu na film</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pokaz kuratorski filmów finałowych</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seans z wyboru dziesiątki, wstęp wolny, spotkanie z twórcami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kopie archiwalne filmów i ich magazyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zachowanie zgłoszonych filmów przez pięć lat, bez publicznego udostępniania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zwiastuny piątki na gali, a przy pokazach przygotowanie techniczne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zwiastuny pięciu filmów na gali</t>
   </si>
   <si>
     <t xml:space="preserve">Podcast towarzyszący Nagrodzie</t>
@@ -196,10 +211,10 @@
     <t xml:space="preserve">bezpłatny materiał edukacyjny</t>
   </si>
   <si>
-    <t xml:space="preserve">sponsor Antologii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razem, wiersze objęte prośbą ("tak")</t>
+    <t xml:space="preserve">sponsor podcastu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razem, wiersze objęte prośbą ("tak" w ostatniej kolumnie)</t>
   </si>
   <si>
     <t xml:space="preserve">Razem, wszystkie wycenione pozycje</t>
@@ -364,7 +379,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -398,10 +413,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -413,18 +432,10 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -437,15 +448,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -701,7 +712,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
@@ -801,10 +812,10 @@
         <v>547809.76</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>77156.8</v>
+        <v>76599.07</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>470652.96</v>
+        <v>471210.69</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>15</v>
@@ -824,13 +835,13 @@
         <v>19</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>62048</v>
+        <v>87808</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>62048</v>
+        <v>87808</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>21</v>
@@ -853,10 +864,10 @@
         <v>162162</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>33942.4</v>
+        <v>33942.51</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>128219.6</v>
+        <v>128219.49</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>24</v>
@@ -881,7 +892,7 @@
       <c r="E9" s="8" t="n">
         <v>183480</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="10" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -928,18 +939,18 @@
         <v>14</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>110960</v>
+        <v>92360</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>28080</v>
+        <v>18480</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>82880</v>
+        <v>73880</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>35</v>
       </c>
     </row>
@@ -954,36 +965,36 @@
         <v>19</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>75000</v>
+        <v>84000</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>75000</v>
+        <v>84000</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>80000</v>
+        <v>89600</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>80000</v>
+        <v>89600</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>20</v>
@@ -991,109 +1002,109 @@
       <c r="G13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>42</v>
+      <c r="D14" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>160912</v>
+        <v>167072</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>17248</v>
+        <v>18480</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>143664</v>
+        <v>148592</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>42</v>
+      <c r="D16" s="12" t="n">
+        <v>8960</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>8960</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="8" t="n">
         <v>4928</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="12" t="n">
         <v>4928</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>16</v>
@@ -1101,10 +1112,10 @@
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>14</v>
@@ -1119,172 +1130,216 @@
         <v>236128</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>42</v>
+      <c r="D19" s="12" t="n">
+        <v>13440</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>13440</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>15176</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>15176</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="10" t="s">
+      <c r="D22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <f aca="false">SUMIFS(D6:D20,$H$6:$H$20,"tak")</f>
-        <v>695032</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <f aca="false">SUMIFS(E6:E20,$H$6:$H$20,"tak")</f>
-        <v>157360</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <f aca="false">SUMIFS(F6:F20,$H$6:$H$20,"tak")</f>
-        <v>537672</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <f aca="false">SUM(D6:D20)</f>
-        <v>1815619.76</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <f aca="false">SUM(E6:E20)</f>
-        <v>511299.2</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <f aca="false">SUM(F6:F20)</f>
-        <v>1304320.56</v>
-      </c>
-    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
+      <c r="A24" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <f aca="false">SUMIF($H$6:$H$22,"tak",D6:D22)</f>
+        <v>738768</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <f aca="false">SUMIF($H$6:$H$22,"tak",E6:E22)</f>
+        <v>158592</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <f aca="false">SUMIF($H$6:$H$22,"tak",F6:F22)</f>
+        <v>580176</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
-        <v>61</v>
+      <c r="A25" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <f aca="false">SUM(D6:D22)</f>
+        <v>1885115.76</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <f aca="false">SUM(E6:E22)</f>
+        <v>511973.58</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <f aca="false">SUM(F6:F22)</f>
+        <v>1373142.18</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
+      <c r="A27" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
+      <c r="A29" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
-        <v>65</v>
+      <c r="A30" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="19" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A28:H28"/>

--- a/attachments/zestawienie-zadania.xlsx
+++ b/attachments/zestawienie-zadania.xlsx
@@ -379,7 +379,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -417,19 +417,11 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -809,13 +801,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>547809.76</v>
+        <v>580289.76</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>76599.07</v>
+        <v>102851.22</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>471210.69</v>
+        <v>477438.54</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>15</v>
@@ -861,13 +853,13 @@
         <v>14</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>162162</v>
+        <v>147862</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>33942.51</v>
+        <v>20881.72</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>128219.49</v>
+        <v>126980.28</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>24</v>
@@ -887,12 +879,12 @@
         <v>27</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>183480</v>
+        <v>167530</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>183480</v>
-      </c>
-      <c r="F9" s="10" t="s">
+        <v>167530</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -939,18 +931,18 @@
         <v>14</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>92360</v>
+        <v>116216</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>18480</v>
+        <v>30800</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>73880</v>
+        <v>85416</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="10" t="s">
         <v>35</v>
       </c>
     </row>
@@ -976,7 +968,7 @@
       <c r="G12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="10" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1002,7 +994,7 @@
       <c r="G13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="10" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1016,19 +1008,19 @@
       <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="9" t="s">
         <v>43</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="10" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1043,18 +1035,18 @@
         <v>14</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>167072</v>
+        <v>190928</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>18480</v>
+        <v>30800</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>148592</v>
+        <v>160128</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="10" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1068,19 +1060,19 @@
       <c r="C16" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="9" t="n">
         <v>8960</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="9" t="n">
         <v>8960</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="10" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1097,10 +1089,10 @@
       <c r="D17" s="8" t="n">
         <v>4928</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="9" t="n">
         <v>4928</v>
       </c>
       <c r="G17" s="6" t="s">
@@ -1121,10 +1113,10 @@
         <v>14</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>268160</v>
+        <v>280480</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>32032</v>
+        <v>44352</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>236128</v>
@@ -1132,7 +1124,7 @@
       <c r="G18" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="10" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1146,19 +1138,19 @@
       <c r="C19" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="9" t="n">
         <v>13440</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="9" t="n">
         <v>13440</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="10" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1172,19 +1164,19 @@
       <c r="C20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="9" t="n">
         <v>15176</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="9" t="n">
         <v>15176</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="10" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1242,95 +1234,95 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="11" t="s">
         <v>64</v>
       </c>
       <c r="D24" s="1" t="n">
         <f aca="false">SUMIF($H$6:$H$22,"tak",D6:D22)</f>
-        <v>738768</v>
+        <v>798800</v>
       </c>
       <c r="E24" s="1" t="n">
         <f aca="false">SUMIF($H$6:$H$22,"tak",E6:E22)</f>
-        <v>158592</v>
+        <v>195552</v>
       </c>
       <c r="F24" s="1" t="n">
         <f aca="false">SUMIF($H$6:$H$22,"tak",F6:F22)</f>
-        <v>580176</v>
+        <v>603248</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="13" t="n">
         <f aca="false">SUM(D6:D22)</f>
-        <v>1885115.76</v>
-      </c>
-      <c r="E25" s="15" t="n">
+        <v>1947377.76</v>
+      </c>
+      <c r="E25" s="13" t="n">
         <f aca="false">SUM(E6:E22)</f>
-        <v>511973.58</v>
-      </c>
-      <c r="F25" s="15" t="n">
+        <v>546174.94</v>
+      </c>
+      <c r="F25" s="13" t="n">
         <f aca="false">SUM(F6:F22)</f>
-        <v>1373142.18</v>
+        <v>1401202.82</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="17" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="17" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="17" t="s">
         <v>70</v>
       </c>
     </row>
